--- a/B7_正規化摘要.xlsx
+++ b/B7_正規化摘要.xlsx
@@ -7,8 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="mask幾何_三種尺度" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="mask幾何_長邊正規化_分組" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="長邊正規化_前後" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="三種尺度_各seed" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="三種尺度_跨seed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="mask幾何_長邊正規化_seed0_分組" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="mask幾何_長邊正規化_seed1_分組" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="mask幾何_長邊正規化_seed2_分組" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="mask幾何_長邊正規化_seed3_分組" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="mask幾何_長邊正規化_seed4_分組" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,76 +420,149 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>尺度</t>
+          <t>方法</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>px/mm CV</t>
+          <t>train_seed</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>X–Y r</t>
+          <t>CV_未正規化</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>CV_正規化後</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>r_未正規化</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>r_正規化後</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>不正規化</t>
+          <t>mask幾何</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.406</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.055</v>
+        <v>0.4058</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0779</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0548</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.6684</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>長邊</t>
+          <t>mask幾何</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.078</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.668</v>
+        <v>0.4041</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.07630000000000001</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0617</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>短邊</t>
+          <t>mask幾何</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.082</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>0.648</v>
+        <v>0.4083</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.0775</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0517</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.6633</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>對角線</t>
+          <t>mask幾何</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.079</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>0.665</v>
+        <v>0.409</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.0502</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6762</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.4073</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.0762</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0522</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.6776</v>
       </c>
     </row>
   </sheetData>
@@ -497,6 +576,615 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>train_seed</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>尺度</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>px/mm CV</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>X–Y r</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>不正規化</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.055</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>長邊</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.668</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>短邊</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.648</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>對角線</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.665</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>不正規化</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.062</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>長邊</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>短邊</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.666</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>對角線</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>不正規化</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.052</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>長邊</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.663</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>短邊</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.642</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>對角線</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.659</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>不正規化</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>長邊</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.676</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>短邊</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.656</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>對角線</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.673</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>不正規化</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.052</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>長邊</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.678</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>短邊</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.655</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>對角線</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.673</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr"/>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>px/mm CV</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>X–Y r</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>尺度</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>不正規化</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.4068</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0542</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0047</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>長邊</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.0766</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.0103</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>短邊</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.08119999999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.6534</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>對角線</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.0774</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0098</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="E1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -687,4 +1375,796 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>整張尺寸</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>張數</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>中位數</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1200x825</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>38</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.156</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.058</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2400x1720</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3" t="n">
+        <v>32.151</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.046</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1200x856</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>31.426</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.061</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1842x1324</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>31.002</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.099</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>787x570</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>23.593</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>789x569</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>27.185</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>790x573</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>29.054</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>797x572</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>28.45</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>803x581</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>26.851</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>804x580</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>25.751</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>823x571</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>25.819</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>整張尺寸</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>張數</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>中位數</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1200x825</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>38</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.078</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2400x1720</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3" t="n">
+        <v>32.036</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.049</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1200x856</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>30.475</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.049</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1842x1324</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>30.459</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.117</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>787x570</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>23.557</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>789x569</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>27.344</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>790x573</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>29.881</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>797x572</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>28.393</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>803x581</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>26.369</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>804x580</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>25.617</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>823x571</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>26.042</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>整張尺寸</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>張數</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>中位數</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1200x825</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>38</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.389</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.057</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2400x1720</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3" t="n">
+        <v>31.882</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.045</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1200x856</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>30.199</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1842x1324</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>30.653</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.102</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>787x570</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>23.332</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>789x569</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>27.178</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>790x573</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>28.93</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>797x572</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>28.026</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>803x581</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>26.346</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>804x580</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>25.485</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>823x571</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>25.901</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>整張尺寸</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>張數</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>中位數</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1200x825</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>38</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.957</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.059</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2400x1720</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3" t="n">
+        <v>31.851</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.047</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1200x856</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>30.845</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.053</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1842x1324</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>30.587</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.104</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>787x570</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>23.706</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>789x569</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>27.181</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>790x573</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>28.517</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>797x572</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>28.602</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>803x581</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>804x580</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>25.442</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>823x571</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>25.926</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>